--- a/Lr14/Calculation Excel Sheet/variants/Transformer_Spec_7p5to1_x1.xlsx
+++ b/Lr14/Calculation Excel Sheet/variants/Transformer_Spec_7p5to1_x1.xlsx
@@ -588,7 +588,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>•   One transformer per set on TDK E 60/22/16 (core PC47EE60-Z, custom coil former, 24 pins).</t>
+          <t>•   One transformer per set on TDK ETD 54/28/19 (core B66395, B66396W coil former, 22 pins).</t>
         </is>
       </c>
     </row>
@@ -650,7 +650,7 @@
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>1 – 3</t>
+          <t>1+2 – 4+5</t>
         </is>
       </c>
       <c r="E12" s="11" t="inlineStr">
@@ -660,7 +660,7 @@
       </c>
       <c r="F12" s="9" t="inlineStr">
         <is>
-          <t>10.4 A   /   18.1 A</t>
+          <t>10.8 A   /   18.2 A</t>
         </is>
       </c>
     </row>
@@ -677,7 +677,7 @@
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>13+14+15 – 16+17+18</t>
+          <t>12+13+14 – 15+16+17+18+19</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
@@ -687,7 +687,7 @@
       </c>
       <c r="F13" s="9" t="inlineStr">
         <is>
-          <t>28.6 A   /   100.2 A</t>
+          <t>28.4 A   /   98.9 A</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>19+20+21 – 22+23+24</t>
+          <t>15+16+17+18+19 – 20+21+22</t>
         </is>
       </c>
       <c r="E14" s="11" t="inlineStr">
@@ -714,7 +714,7 @@
       </c>
       <c r="F14" s="9" t="inlineStr">
         <is>
-          <t>28.6 A   /   100.2 A</t>
+          <t>28.4 A   /   98.9 A</t>
         </is>
       </c>
     </row>
@@ -731,7 +731,7 @@
       </c>
       <c r="D15" s="9" t="inlineStr">
         <is>
-          <t>10 – 12</t>
+          <t>8 – 10</t>
         </is>
       </c>
       <c r="E15" s="11" t="inlineStr">
@@ -741,21 +741,21 @@
       </c>
       <c r="F15" s="9" t="inlineStr">
         <is>
-          <t>104 mA dc load (VCC)</t>
+          <t>92 mA dc load (VCC)</t>
         </is>
       </c>
     </row>
     <row r="17" ht="14" customHeight="1">
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>Centre tap is made on the PCB by joining pins 16, 17, 18, 19, 20 and 21 — do NOT join them inside the transformer.   Three pins per secondary terminal, one per Litz bundle: confirm the pin current rating.</t>
+          <t>Centre tap: NS2 finish and NS3 start share pins 15, 16, 17, 18 and 19, one Litz bundle of each on a pin.   At most two bundles on a pin: confirm the pin current rating.   NP1: the 3 bundles of a turn are turned over as a group at each layer.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="14" customHeight="1">
       <c r="B18" s="12" t="inlineStr">
         <is>
-          <t>Custom coil former for E 60/22/16, 24 pins, made to this specification.   Pin numbers count along one row from pin 1 and back along the other — confirm on the bobbin drawing before winding.</t>
+          <t>Coil former TDK B66396W (ETD 54/28/19), 22 pins, with a 2.0 mm partition added between the two sections.   Pin numbers count along one row from pin 1 and back along the other — confirm on the bobbin drawing before winding.</t>
         </is>
       </c>
     </row>
@@ -817,12 +817,12 @@
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>1 – 3</t>
+          <t>1+2 – 4+5</t>
         </is>
       </c>
       <c r="E22" s="11" t="inlineStr">
         <is>
-          <t>39.46 µH    ±10 %</t>
+          <t>65.95 µH    ±10 %</t>
         </is>
       </c>
       <c r="F22" s="10" t="inlineStr">
@@ -844,12 +844,12 @@
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
-          <t>1 – 3</t>
+          <t>1+2 – 4+5</t>
         </is>
       </c>
       <c r="E23" s="11" t="inlineStr">
         <is>
-          <t>14.00 µH    ±10 %</t>
+          <t>23.40 µH    ±10 %</t>
         </is>
       </c>
       <c r="F23" s="10" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>1 – 3</t>
+          <t>1+2 – 4+5</t>
         </is>
       </c>
       <c r="E24" s="11" t="inlineStr">
@@ -881,14 +881,14 @@
       </c>
       <c r="F24" s="10" t="inlineStr">
         <is>
-          <t>Test current 14 A, normal temperature</t>
+          <t>Test current 16 A, normal temperature</t>
         </is>
       </c>
     </row>
     <row r="25" ht="14" customHeight="1">
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>Both measured at 1 – 3 of ONE transformer.   Item 2 is set by the winding and the partition between the two sections: measure it, and each half alone, on the first samples; a thinner partition lowers it.</t>
+          <t>Both measured at 1+2 – 4+5 of ONE transformer.   Item 2 is set by the winding and the partition between the two sections: measure it, and each half alone, on the first samples; a thinner partition lowers it.</t>
         </is>
       </c>
     </row>
@@ -923,7 +923,7 @@
       </c>
       <c r="E29" s="14" t="inlineStr">
         <is>
-          <t>92  to  212 kHz</t>
+          <t>45  to  120 kHz</t>
         </is>
       </c>
       <c r="F29" s="12" t="inlineStr">
@@ -945,7 +945,7 @@
       </c>
       <c r="E30" s="14" t="inlineStr">
         <is>
-          <t>Ae  ≥  116 mm²</t>
+          <t>Ae  ≥  212 mm²</t>
         </is>
       </c>
       <c r="F30" s="12" t="inlineStr">
